--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119941757</v>
+        <v>119941760</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565474</v>
+        <v>565548</v>
       </c>
       <c r="R2" t="n">
-        <v>6411164</v>
+        <v>6411154</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941760</v>
+        <v>119941766</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>74577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,47 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565548</v>
+        <v>565430</v>
       </c>
       <c r="R4" t="n">
-        <v>6411154</v>
+        <v>6411122</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941761</v>
+        <v>119941759</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1043,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565602</v>
+        <v>565482</v>
       </c>
       <c r="R5" t="n">
-        <v>6411170</v>
+        <v>6411162</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,6 +1084,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941766</v>
+        <v>119941761</v>
       </c>
       <c r="B6" t="n">
-        <v>74577</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,38 +1127,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565430</v>
+        <v>565602</v>
       </c>
       <c r="R6" t="n">
-        <v>6411122</v>
+        <v>6411170</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1226,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941759</v>
+        <v>119941757</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1256,7 +1261,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1270,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565482</v>
+        <v>565474</v>
       </c>
       <c r="R7" t="n">
-        <v>6411162</v>
+        <v>6411164</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1306,11 +1311,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119941760</v>
+        <v>119941757</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565548</v>
+        <v>565474</v>
       </c>
       <c r="R2" t="n">
-        <v>6411154</v>
+        <v>6411164</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119941762</v>
+        <v>119941759</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565661</v>
+        <v>565482</v>
       </c>
       <c r="R3" t="n">
-        <v>6411196</v>
+        <v>6411162</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941766</v>
+        <v>119941761</v>
       </c>
       <c r="B4" t="n">
-        <v>74577</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +914,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565430</v>
+        <v>565602</v>
       </c>
       <c r="R4" t="n">
-        <v>6411122</v>
+        <v>6411170</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941759</v>
+        <v>119941766</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>74577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,47 +1025,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565482</v>
+        <v>565430</v>
       </c>
       <c r="R5" t="n">
-        <v>6411162</v>
+        <v>6411122</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,11 +1089,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941761</v>
+        <v>119941760</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565602</v>
+        <v>565548</v>
       </c>
       <c r="R6" t="n">
-        <v>6411170</v>
+        <v>6411154</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941757</v>
+        <v>119941762</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565474</v>
+        <v>565661</v>
       </c>
       <c r="R7" t="n">
-        <v>6411164</v>
+        <v>6411196</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119941759</v>
+        <v>119941762</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565482</v>
+        <v>565661</v>
       </c>
       <c r="R3" t="n">
-        <v>6411162</v>
+        <v>6411196</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1013,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941766</v>
+        <v>119941760</v>
       </c>
       <c r="B5" t="n">
-        <v>74577</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,38 +1020,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565430</v>
+        <v>565548</v>
       </c>
       <c r="R5" t="n">
-        <v>6411122</v>
+        <v>6411154</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941760</v>
+        <v>119941759</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1150,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565548</v>
+        <v>565482</v>
       </c>
       <c r="R6" t="n">
-        <v>6411154</v>
+        <v>6411162</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,6 +1204,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941762</v>
+        <v>119941766</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>74577</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,47 +1247,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565661</v>
+        <v>565430</v>
       </c>
       <c r="R7" t="n">
-        <v>6411196</v>
+        <v>6411122</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941761</v>
+        <v>119941760</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565602</v>
+        <v>565548</v>
       </c>
       <c r="R4" t="n">
-        <v>6411170</v>
+        <v>6411154</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941760</v>
+        <v>119941761</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565548</v>
+        <v>565602</v>
       </c>
       <c r="R5" t="n">
-        <v>6411154</v>
+        <v>6411170</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941760</v>
+        <v>119941761</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565548</v>
+        <v>565602</v>
       </c>
       <c r="R4" t="n">
-        <v>6411154</v>
+        <v>6411170</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941761</v>
+        <v>119941760</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565602</v>
+        <v>565548</v>
       </c>
       <c r="R5" t="n">
-        <v>6411170</v>
+        <v>6411154</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119941757</v>
+        <v>119941759</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565474</v>
+        <v>565482</v>
       </c>
       <c r="R2" t="n">
-        <v>6411164</v>
+        <v>6411162</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119941762</v>
+        <v>119941766</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>74593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,47 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565661</v>
+        <v>565430</v>
       </c>
       <c r="R3" t="n">
-        <v>6411196</v>
+        <v>6411122</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941761</v>
+        <v>119941760</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565602</v>
+        <v>565548</v>
       </c>
       <c r="R4" t="n">
-        <v>6411170</v>
+        <v>6411154</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941760</v>
+        <v>119941762</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,7 +1039,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565548</v>
+        <v>565661</v>
       </c>
       <c r="R5" t="n">
-        <v>6411154</v>
+        <v>6411196</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941759</v>
+        <v>119941757</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,7 +1150,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1168,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565482</v>
+        <v>565474</v>
       </c>
       <c r="R6" t="n">
-        <v>6411162</v>
+        <v>6411164</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,11 +1200,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941766</v>
+        <v>119941761</v>
       </c>
       <c r="B7" t="n">
-        <v>74577</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,38 +1238,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565430</v>
+        <v>565602</v>
       </c>
       <c r="R7" t="n">
-        <v>6411122</v>
+        <v>6411170</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119941759</v>
+        <v>119941757</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565482</v>
+        <v>565474</v>
       </c>
       <c r="R2" t="n">
-        <v>6411162</v>
+        <v>6411164</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,11 +760,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119941766</v>
+        <v>119941759</v>
       </c>
       <c r="B3" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565430</v>
+        <v>565482</v>
       </c>
       <c r="R3" t="n">
-        <v>6411122</v>
+        <v>6411162</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1115,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941757</v>
+        <v>119941766</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,47 +1136,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565474</v>
+        <v>565430</v>
       </c>
       <c r="R6" t="n">
-        <v>6411164</v>
+        <v>6411122</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119941757</v>
+        <v>119941761</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565474</v>
+        <v>565602</v>
       </c>
       <c r="R2" t="n">
-        <v>6411164</v>
+        <v>6411170</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119941759</v>
+        <v>119941762</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565482</v>
+        <v>565661</v>
       </c>
       <c r="R3" t="n">
-        <v>6411162</v>
+        <v>6411196</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941760</v>
+        <v>119941759</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -937,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565548</v>
+        <v>565482</v>
       </c>
       <c r="R4" t="n">
-        <v>6411154</v>
+        <v>6411162</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,6 +982,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941762</v>
+        <v>119941760</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565661</v>
+        <v>565548</v>
       </c>
       <c r="R5" t="n">
-        <v>6411196</v>
+        <v>6411154</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941761</v>
+        <v>119941757</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565602</v>
+        <v>565474</v>
       </c>
       <c r="R7" t="n">
-        <v>6411170</v>
+        <v>6411164</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941760</v>
+        <v>119941766</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,47 +1025,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565548</v>
+        <v>565430</v>
       </c>
       <c r="R5" t="n">
-        <v>6411154</v>
+        <v>6411122</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941766</v>
+        <v>119941760</v>
       </c>
       <c r="B6" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,38 +1127,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565430</v>
+        <v>565548</v>
       </c>
       <c r="R6" t="n">
-        <v>6411122</v>
+        <v>6411154</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119941762</v>
+        <v>119941760</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565661</v>
+        <v>565548</v>
       </c>
       <c r="R3" t="n">
-        <v>6411196</v>
+        <v>6411154</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941759</v>
+        <v>119941757</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565482</v>
+        <v>565474</v>
       </c>
       <c r="R4" t="n">
-        <v>6411162</v>
+        <v>6411164</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,11 +982,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1115,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941760</v>
+        <v>119941759</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1150,7 +1145,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565548</v>
+        <v>565482</v>
       </c>
       <c r="R6" t="n">
-        <v>6411154</v>
+        <v>6411162</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,6 +1195,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,7 +1226,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941757</v>
+        <v>119941762</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565474</v>
+        <v>565661</v>
       </c>
       <c r="R7" t="n">
-        <v>6411164</v>
+        <v>6411196</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119941761</v>
+        <v>119941766</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565602</v>
+        <v>565430</v>
       </c>
       <c r="R2" t="n">
-        <v>6411170</v>
+        <v>6411122</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941757</v>
+        <v>119941761</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -932,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565474</v>
+        <v>565602</v>
       </c>
       <c r="R4" t="n">
-        <v>6411164</v>
+        <v>6411170</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941766</v>
+        <v>119941762</v>
       </c>
       <c r="B5" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1011,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565430</v>
+        <v>565661</v>
       </c>
       <c r="R5" t="n">
-        <v>6411122</v>
+        <v>6411196</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941762</v>
+        <v>119941757</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565661</v>
+        <v>565474</v>
       </c>
       <c r="R7" t="n">
-        <v>6411196</v>
+        <v>6411164</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119941766</v>
+        <v>119941759</v>
       </c>
       <c r="B2" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565430</v>
+        <v>565482</v>
       </c>
       <c r="R2" t="n">
-        <v>6411122</v>
+        <v>6411162</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119941760</v>
+        <v>119941762</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -812,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565548</v>
+        <v>565661</v>
       </c>
       <c r="R3" t="n">
-        <v>6411154</v>
+        <v>6411196</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941761</v>
+        <v>119941760</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -923,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -937,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565602</v>
+        <v>565548</v>
       </c>
       <c r="R4" t="n">
-        <v>6411170</v>
+        <v>6411154</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941762</v>
+        <v>119941757</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1034,7 +1048,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565661</v>
+        <v>565474</v>
       </c>
       <c r="R5" t="n">
-        <v>6411196</v>
+        <v>6411164</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941759</v>
+        <v>119941761</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1145,7 +1159,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565482</v>
+        <v>565602</v>
       </c>
       <c r="R6" t="n">
-        <v>6411162</v>
+        <v>6411170</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,11 +1209,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941757</v>
+        <v>119941766</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,47 +1247,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565474</v>
+        <v>565430</v>
       </c>
       <c r="R7" t="n">
-        <v>6411164</v>
+        <v>6411122</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119941759</v>
+        <v>119941766</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565482</v>
+        <v>565430</v>
       </c>
       <c r="R2" t="n">
-        <v>6411162</v>
+        <v>6411122</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119941762</v>
+        <v>119941761</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -826,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565661</v>
+        <v>565602</v>
       </c>
       <c r="R3" t="n">
-        <v>6411196</v>
+        <v>6411170</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -902,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119941760</v>
+        <v>119941757</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -937,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565548</v>
+        <v>565474</v>
       </c>
       <c r="R4" t="n">
-        <v>6411154</v>
+        <v>6411164</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1013,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941757</v>
+        <v>119941762</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1048,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1062,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565474</v>
+        <v>565661</v>
       </c>
       <c r="R5" t="n">
-        <v>6411164</v>
+        <v>6411196</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941761</v>
+        <v>119941759</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1159,7 +1145,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1173,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565602</v>
+        <v>565482</v>
       </c>
       <c r="R6" t="n">
-        <v>6411170</v>
+        <v>6411162</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,6 +1195,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941766</v>
+        <v>119941760</v>
       </c>
       <c r="B7" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,38 +1238,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565430</v>
+        <v>565548</v>
       </c>
       <c r="R7" t="n">
-        <v>6411122</v>
+        <v>6411154</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 36077-2021 artfynd.xlsx
+++ b/artfynd/A 36077-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>119941766</v>
       </c>
       <c r="B2" t="n">
-        <v>74593</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -777,59 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119941761</v>
+        <v>119941770</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Västergöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565602</v>
+        <v>565522</v>
       </c>
       <c r="R3" t="n">
-        <v>6411170</v>
+        <v>6411189</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,12 +872,7 @@
         <v>119941757</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119941762</v>
+        <v>119941759</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,7 +1005,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565661</v>
+        <v>565482</v>
       </c>
       <c r="R5" t="n">
-        <v>6411196</v>
+        <v>6411162</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,6 +1055,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,15 +1086,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119941759</v>
+        <v>119941760</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,7 +1116,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565482</v>
+        <v>565548</v>
       </c>
       <c r="R6" t="n">
-        <v>6411162</v>
+        <v>6411154</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,11 +1166,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca antal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,15 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119941760</v>
+        <v>119941761</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1222,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565548</v>
+        <v>565602</v>
       </c>
       <c r="R7" t="n">
-        <v>6411154</v>
+        <v>6411170</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,6 +1295,112 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119941762</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Söder om Västergöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>565661</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6411196</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
